--- a/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/车辆信息模版.xlsx
+++ b/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/车辆信息模版.xlsx
@@ -98,7 +98,7 @@
     <t>Breakpoint Time</t>
   </si>
   <si>
-    <t>黄色背景数据为示例数据，导入时请从第三行开始录入数据。
+    <t>黄色背景数据为示例数据，导入时请从第四行开始录入数据。
 The data with a yellow background is sample data. When importing, please start entering data from the third row.</t>
   </si>
   <si>
@@ -808,12 +808,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1384,149 +1381,149 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:23">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>1288</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>45800.5231828704</v>
       </c>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="6">
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="5">
         <v>45800.5231828704</v>
       </c>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="6">
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="5">
         <v>45800.5231828704</v>
       </c>
     </row>

--- a/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/车辆信息模版.xlsx
+++ b/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/车辆信息模版.xlsx
@@ -27,15 +27,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>VIN</t>
   </si>
   <si>
+    <t>COC Template No.</t>
+  </si>
+  <si>
+    <t>tvv</t>
+  </si>
+  <si>
+    <t>Material No</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Model No.</t>
+  </si>
+  <si>
     <t>Vehicle Model</t>
   </si>
   <si>
-    <t>Material No</t>
+    <t>Factory Code</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Secondary Color</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Manufacture Date</t>
+  </si>
+  <si>
+    <t>Issue Date</t>
+  </si>
+  <si>
+    <t>Engine Number</t>
+  </si>
+  <si>
+    <t>Battery Number</t>
+  </si>
+  <si>
+    <t>Motor Number</t>
+  </si>
+  <si>
+    <t>tire</t>
   </si>
   <si>
     <t>Brand</t>
@@ -47,89 +89,68 @@
     <t>Sale Name</t>
   </si>
   <si>
-    <t>tire</t>
-  </si>
-  <si>
-    <t>Project Name</t>
+    <t>Tire resistance grade</t>
+  </si>
+  <si>
+    <t>Sale company Name</t>
   </si>
   <si>
     <t>Customer No</t>
   </si>
   <si>
-    <t>Tire Resistance Grade</t>
-  </si>
-  <si>
-    <t>Factory Code</t>
-  </si>
-  <si>
-    <t>Factory Name</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Color</t>
-  </si>
-  <si>
-    <t>Secondary Color</t>
-  </si>
-  <si>
-    <t>Issue Date</t>
-  </si>
-  <si>
-    <t>Certificate Version</t>
-  </si>
-  <si>
-    <t>tvv</t>
-  </si>
-  <si>
-    <t>Manufacture Date</t>
-  </si>
-  <si>
-    <t>Engine Number</t>
-  </si>
-  <si>
-    <t>Battery Number</t>
-  </si>
-  <si>
-    <t>Motor Number</t>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Validate result</t>
+  </si>
+  <si>
+    <t>XML Status</t>
+  </si>
+  <si>
+    <t>First vehicle validate</t>
   </si>
   <si>
     <t>Breakpoint Time</t>
   </si>
   <si>
-    <t>黄色背景数据为示例数据，导入时请从第四行开始录入数据。
-The data with a yellow background is sample data. When importing, please start entering data from the third row.</t>
+    <t>黄色背景数据为示例数据，导入时请从第四行开始录入数据。红色表头为必填数据项。
+The data with a yellow background is sample data. When importing, please start entering data from the third row.Red headers indicate required data fields.</t>
   </si>
   <si>
     <t>LVUGTBHDXTD903001</t>
   </si>
   <si>
+    <t>COC0001</t>
+  </si>
+  <si>
+    <t>TEST_MAT_HEV_M1_001</t>
+  </si>
+  <si>
+    <t>SQR6470T18TBE</t>
+  </si>
+  <si>
     <t>M1</t>
   </si>
   <si>
-    <t>TEST_MAT_HEV_M1_001</t>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>GX</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>OMODA</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>C100283746928374</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>Factory Of A3</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>BW</t>
-  </si>
-  <si>
-    <t>GX</t>
   </si>
 </sst>
 </file>
@@ -142,7 +163,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,9 +180,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="9"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -311,12 +338,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -542,9 +575,15 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -678,55 +717,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -741,90 +777,102 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1352,33 +1400,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="20.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="18.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="21.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="13.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="16.7777777777778" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="27.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="17.6666666666667" customWidth="1"/>
-    <col min="12" max="12" width="15.3333333333333" customWidth="1"/>
-    <col min="15" max="15" width="21.3333333333333" customWidth="1"/>
-    <col min="16" max="16" width="17.2222222222222" customWidth="1"/>
-    <col min="17" max="17" width="32.2222222222222" customWidth="1"/>
-    <col min="19" max="19" width="25.7777777777778" customWidth="1"/>
-    <col min="20" max="20" width="21.8888888888889" customWidth="1"/>
-    <col min="21" max="21" width="22" customWidth="1"/>
-    <col min="22" max="22" width="16.8888888888889" customWidth="1"/>
-    <col min="23" max="23" width="20.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="22.4444444444444" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1111111111111" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1111111111111" customWidth="1"/>
+    <col min="5" max="5" width="18.1111111111111" hidden="1" customWidth="1"/>
+    <col min="6" max="9" width="18.1111111111111" customWidth="1"/>
+    <col min="10" max="11" width="19.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="22.2222222222222" customWidth="1"/>
+    <col min="13" max="13" width="19.3333333333333" customWidth="1"/>
+    <col min="14" max="14" width="18.8888888888889" customWidth="1"/>
+    <col min="15" max="15" width="18.8888888888889" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="26.2222222222222" customWidth="1"/>
+    <col min="17" max="17" width="8.88888888888889" hidden="1" customWidth="1"/>
+    <col min="18" max="20" width="16" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="31.8888888888889" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="25.4444444444444" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="16" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="21.8888888888889" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="16" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="35.5555555555556" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="20.2222222222222" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:23">
+    <row r="1" ht="23" customHeight="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1387,13 +1440,13 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1402,7 +1455,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1414,122 +1467,152 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" ht="34" customHeight="1" spans="1:23">
-      <c r="A2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
+    <row r="2" ht="34" customHeight="1" spans="1:28">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
       <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
     </row>
-    <row r="3" spans="1:23">
-      <c r="A3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="4">
+    <row r="3" spans="1:28">
+      <c r="A3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="8">
+        <v>45800.5231828704</v>
+      </c>
+      <c r="M3" s="8">
+        <v>45800.5231828704</v>
+      </c>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" s="5">
         <v>1288</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="5">
-        <v>45800.5231828704</v>
-      </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="5">
-        <v>45800.5231828704</v>
-      </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="5">
+      <c r="T3" s="5"/>
+      <c r="U3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="8">
         <v>45800.5231828704</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:W2"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="R2:AB2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
